--- a/Descargas/PF-Com.xlsx
+++ b/Descargas/PF-Com.xlsx
@@ -1080,13 +1080,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{845D9602-C0DC-4295-9AC5-D1457E990119}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{710B1640-26F5-4B34-A524-5656F5206A21}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D101D9F-7323-455B-8D86-5AC66978B7D6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{44C1907C-5607-470C-BB1B-9642852A9647}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F134B3F5-FC74-4664-B601-B856067E2FAE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D6F285B-CA37-44FF-893E-BF51F1CDD723}"/>
 </file>